--- a/Excel_Solo_Valores.xlsx
+++ b/Excel_Solo_Valores.xlsx
@@ -3541,31 +3541,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BRUNO BAEZ</v>
+        <v>LEO CAMACHO</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D2">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="E2">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="F2">
         <v>9.9</v>
       </c>
       <c r="G2">
-        <v>9.3</v>
+        <v>9.9</v>
       </c>
       <c r="H2">
-        <v>9.3</v>
+        <v>9.9</v>
       </c>
       <c r="I2">
-        <v>50.7</v>
+        <v>53.4</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MAURO REGAND</v>
+        <v>EMI</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D3">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="E3">
         <v>9.9</v>
@@ -3594,13 +3594,13 @@
         <v>9.9</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="H3">
         <v>9.6</v>
       </c>
       <c r="I3">
-        <v>51</v>
+        <v>52.800000000000004</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -3611,31 +3611,31 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">ALFREDO </v>
+        <v>SANTI CAMACHO</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
       <c r="C4">
-        <v>9.3</v>
+        <v>9.9</v>
       </c>
       <c r="D4">
+        <v>9.6</v>
+      </c>
+      <c r="E4">
         <v>9.9</v>
-      </c>
-      <c r="E4">
-        <v>9.6</v>
       </c>
       <c r="F4">
         <v>9.9</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="H4">
-        <v>9.3</v>
+        <v>9.9</v>
       </c>
       <c r="I4">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -3646,19 +3646,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ELIEL</v>
+        <v>DIEGO CHAVEZ</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D5">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="E5">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="F5">
         <v>9.9</v>
@@ -3667,10 +3667,10 @@
         <v>9.6</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="I5">
-        <v>51.300000000000004</v>
+        <v>52.8</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>JOSE MARIA</v>
+        <v>NICO FLORES</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -3690,22 +3690,22 @@
         <v>9.6</v>
       </c>
       <c r="D6">
-        <v>9.3</v>
+        <v>9.6</v>
       </c>
       <c r="E6">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="F6">
         <v>9.9</v>
       </c>
       <c r="G6">
-        <v>9.3</v>
+        <v>9.6</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="I6">
-        <v>51.300000000000004</v>
+        <v>52.5</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -3716,19 +3716,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CARLOS AZNAR</v>
+        <v>DIEGO CUEVAS</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D7">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="E7">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="F7">
         <v>9.9</v>
@@ -3740,7 +3740,7 @@
         <v>9.6</v>
       </c>
       <c r="I7">
-        <v>51.300000000000004</v>
+        <v>52.5</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -3757,10 +3757,10 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>9.3</v>
+        <v>9.9</v>
       </c>
       <c r="D8">
-        <v>9.3</v>
+        <v>9.6</v>
       </c>
       <c r="E8">
         <v>9.6</v>
@@ -3769,13 +3769,13 @@
         <v>9.9</v>
       </c>
       <c r="G8">
-        <v>9.3</v>
+        <v>9.6</v>
       </c>
       <c r="H8">
         <v>9.9</v>
       </c>
       <c r="I8">
-        <v>51.300000000000004</v>
+        <v>52.5</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>EMI</v>
+        <v>ELIEL</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -3798,19 +3798,19 @@
         <v>9.6</v>
       </c>
       <c r="E9">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="F9">
         <v>9.9</v>
       </c>
       <c r="G9">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="H9">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="I9">
-        <v>51.6</v>
+        <v>52.49999999999999</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>DIEGO CUEVAS</v>
+        <v>JOSE MARIA</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10">
-        <v>9.3</v>
+        <v>9.6</v>
       </c>
       <c r="D10">
         <v>9.6</v>
       </c>
       <c r="E10">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="F10">
         <v>9.9</v>
@@ -3842,10 +3842,10 @@
         <v>9.3</v>
       </c>
       <c r="H10">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="I10">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -3856,16 +3856,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>DIEGO CHAVEZ</v>
+        <v>CARLOS AZNAR</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
       <c r="C11">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="E11">
         <v>9.6</v>
@@ -3877,7 +3877,7 @@
         <v>9.6</v>
       </c>
       <c r="H11">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="I11">
         <v>51.9</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>NICO FLORES</v>
+        <v>MAURO REGAND</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -3909,10 +3909,10 @@
         <v>9.9</v>
       </c>
       <c r="G12">
-        <v>9.6</v>
+        <v>9.3</v>
       </c>
       <c r="H12">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="I12">
         <v>51.9</v>
@@ -3926,31 +3926,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SANTI CAMACHO</v>
+        <v xml:space="preserve">ALFREDO </v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
       <c r="C13">
-        <v>9.6</v>
+        <v>9.3</v>
       </c>
       <c r="D13">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="E13">
-        <v>9.9</v>
+        <v>9.3</v>
       </c>
       <c r="F13">
         <v>9.9</v>
       </c>
       <c r="G13">
-        <v>9.6</v>
+        <v>9.3</v>
       </c>
       <c r="H13">
         <v>9.6</v>
       </c>
       <c r="I13">
-        <v>52.2</v>
+        <v>51.300000000000004</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -3961,31 +3961,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LEO CAMACHO</v>
+        <v>BRUNO BAEZ</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
       <c r="C14">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="E14">
-        <v>9.9</v>
+        <v>9.3</v>
       </c>
       <c r="F14">
         <v>9.9</v>
       </c>
       <c r="G14">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="H14">
         <v>9.6</v>
       </c>
       <c r="I14">
-        <v>52.800000000000004</v>
+        <v>50.400000000000006</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -3996,31 +3996,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>PATRICIO</v>
+        <v>BRUNO JACOBO</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="E15">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="F15">
         <v>9.9</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="H15">
         <v>9</v>
       </c>
       <c r="I15">
-        <v>49.5</v>
+        <v>52.2</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -4031,16 +4031,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>BRITAN AKIM</v>
+        <v>NICOLAS CAPITANACCI</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16">
-        <v>9.3</v>
+        <v>9.6</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="E16">
         <v>9.6</v>
@@ -4049,13 +4049,13 @@
         <v>9.9</v>
       </c>
       <c r="G16">
-        <v>9</v>
+        <v>9.3</v>
       </c>
       <c r="H16">
         <v>9</v>
       </c>
       <c r="I16">
-        <v>49.8</v>
+        <v>51.3</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>NICOLAS CAPITANACCI</v>
+        <v>BRITAN AKIM</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -4087,10 +4087,10 @@
         <v>9.3</v>
       </c>
       <c r="H17">
-        <v>9</v>
+        <v>9.3</v>
       </c>
       <c r="I17">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -4101,7 +4101,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>BRUNO JACOBO</v>
+        <v>PATRICIO</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -4110,10 +4110,10 @@
         <v>9.3</v>
       </c>
       <c r="D18">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="F18">
         <v>9.9</v>
@@ -4125,7 +4125,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>51.3</v>
+        <v>50.099999999999994</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -4142,25 +4142,25 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>9.3</v>
       </c>
       <c r="F19">
         <v>9.9</v>
       </c>
       <c r="G19">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="H19">
-        <v>9</v>
+        <v>9.3</v>
       </c>
       <c r="I19">
-        <v>48.9</v>
+        <v>51.60000000000001</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>MARIO</v>
+        <v>SANTIAGO SIGLER</v>
       </c>
       <c r="B20">
         <v>6</v>
@@ -4180,22 +4180,22 @@
         <v>9.3</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="F20">
         <v>9.6</v>
       </c>
       <c r="G20">
-        <v>9</v>
+        <v>9.3</v>
       </c>
       <c r="H20">
-        <v>9.6</v>
+        <v>9.3</v>
       </c>
       <c r="I20">
-        <v>49.5</v>
+        <v>51</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -4206,7 +4206,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SANTIAGO SIGLER</v>
+        <v>MARIO</v>
       </c>
       <c r="B21">
         <v>6</v>
@@ -4224,13 +4224,13 @@
         <v>9.6</v>
       </c>
       <c r="G21">
-        <v>9.3</v>
+        <v>9.6</v>
       </c>
       <c r="H21">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="I21">
-        <v>50.099999999999994</v>
+        <v>51</v>
       </c>
       <c r="J21" t="str">
         <v/>

--- a/Excel_Solo_Valores.xlsx
+++ b/Excel_Solo_Valores.xlsx
@@ -2009,13 +2009,13 @@
         <v>AA NP</v>
       </c>
       <c r="E1" t="str">
-        <v>73.9</v>
+        <v>74.6</v>
       </c>
       <c r="F1" t="str">
         <v>AA</v>
       </c>
       <c r="G1" t="str">
-        <v>69.4</v>
+        <v>70.1</v>
       </c>
       <c r="H1" t="str">
         <v>72.46%</v>
@@ -2106,10 +2106,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F3">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -2203,7 +2203,7 @@
         <v>1.6</v>
       </c>
       <c r="G5">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="H5">
         <v>0.8</v>
@@ -2326,19 +2326,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Arabesca</v>
+        <v>Giro y medio ad ext</v>
       </c>
       <c r="B8">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="E8">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Doble giro atras</v>
+        <v>Doble giro atrás LC</v>
       </c>
       <c r="B9">
         <v>9</v>
@@ -2576,10 +2576,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F13">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G13">
-        <v>12.9</v>
+        <v>13.299999999999999</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -2670,10 +2670,10 @@
         <v>0.1</v>
       </c>
       <c r="F15">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G15">
-        <v>11.4</v>
+        <v>11.799999999999999</v>
       </c>
       <c r="H15">
         <v>0.7</v>
@@ -2937,19 +2937,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Finlandesa</v>
+        <v>Triple rusa a Flank</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C21">
         <v>4</v>
       </c>
       <c r="D21" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="E21">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -3046,10 +3046,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F23">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="G23">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>1.4</v>
       </c>
       <c r="G25">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="H25">
         <v>0.9</v>
@@ -3219,19 +3219,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Inglesa</v>
+        <v>Dominada adelante a Lsit</v>
       </c>
       <c r="B27">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E27">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -4300,7 +4300,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Molino</v>
+        <v>Gigante</v>
       </c>
       <c r="B50">
         <v>13</v>
@@ -4347,19 +4347,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Endo</v>
+        <v>Cambio directo</v>
       </c>
       <c r="B51">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E51">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F51" t="str">
         <v/>
@@ -4394,10 +4394,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Cambio sencillo</v>
+        <v>Molino</v>
       </c>
       <c r="B52">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -4441,19 +4441,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Gigante</v>
+        <v>Endo</v>
       </c>
       <c r="B53">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E53">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F53" t="str">
         <v>BPS</v>
@@ -4655,7 +4655,7 @@
         <v>Valor decimal</v>
       </c>
       <c r="F3">
-        <v>2.0000000000000004</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>13.4</v>
@@ -4687,13 +4687,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Doble en V atrás</v>
+        <v>Doble adelante en c</v>
       </c>
       <c r="B4">
         <v>16</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="str">
         <v>D</v>
@@ -4734,13 +4734,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Doble adelante en c</v>
+        <v>Doble en V atrás</v>
       </c>
       <c r="B5">
         <v>16</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="str">
         <v>D</v>
@@ -4781,19 +4781,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Giro al frente extendido LC</v>
+        <v>Flick Flack LC</v>
       </c>
       <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
       <c r="D6" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="E6">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -4828,19 +4828,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Arabesca</v>
+        <v>Giro atrás LC</v>
       </c>
       <c r="B7">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -4875,19 +4875,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Doble en c atrás</v>
+        <v>Arabesca</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="E8">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -4922,19 +4922,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Giro atrás LC</v>
+        <v>Giro al frente ext</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -4969,19 +4969,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Flick Flack</v>
+        <v>Mortal Ext ade</v>
       </c>
       <c r="B10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="str">
         <v>BPP</v>
@@ -5016,19 +5016,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Mortal Ext atrás</v>
+        <v>Doble en c atrás</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E11">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -7095,25 +7095,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>70</v>
+        <v>ALONSO</v>
       </c>
       <c r="B1" t="str">
-        <v>ALONSO</v>
+        <v>__EMPTY</v>
       </c>
       <c r="C1" t="str">
-        <v>__EMPTY</v>
+        <v>N 10</v>
       </c>
       <c r="D1" t="str">
-        <v>N 10</v>
+        <v>AA NP</v>
       </c>
       <c r="E1" t="str">
-        <v>AA NP</v>
+        <v>78.9</v>
       </c>
       <c r="F1" t="str">
-        <v>78.8</v>
+        <v>AA</v>
       </c>
       <c r="G1" t="str">
-        <v>AA</v>
+        <v>70.1</v>
       </c>
       <c r="H1" t="str">
         <v>74.90%</v>
@@ -7181,25 +7181,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>PISO</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>ALONSO</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>NOTA D</v>
+      </c>
+      <c r="G2" t="str">
         <v>NP</v>
-      </c>
-      <c r="B2" t="str">
-        <v>PISO</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v>ALONSO</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>NOTA D</v>
       </c>
       <c r="H2" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -7266,26 +7266,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
+        <v>NOMBRE</v>
+      </c>
+      <c r="B3" t="str">
+        <v>NÚM DE ID</v>
+      </c>
+      <c r="C3" t="str">
+        <v>GRUPO</v>
+      </c>
+      <c r="D3" t="str">
+        <v>VALOR</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Valor decimal</v>
+      </c>
+      <c r="F3">
+        <v>2.5</v>
+      </c>
+      <c r="G3">
         <v>14.5</v>
-      </c>
-      <c r="B3" t="str">
-        <v>NOMBRE</v>
-      </c>
-      <c r="C3" t="str">
-        <v>NÚM DE ID</v>
-      </c>
-      <c r="D3" t="str">
-        <v>GRUPO</v>
-      </c>
-      <c r="E3" t="str">
-        <v>VALOR</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Valor decimal</v>
-      </c>
-      <c r="G3">
-        <v>2.5</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -7353,25 +7353,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>Doble adelante en c</v>
+      </c>
+      <c r="B4">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>D</v>
+      </c>
+      <c r="E4">
+        <v>0.4</v>
+      </c>
+      <c r="F4" t="str">
+        <v>GRUPOS</v>
+      </c>
+      <c r="G4" t="str">
         <v>Probable NF</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Doble adelante en c</v>
-      </c>
-      <c r="C4">
-        <v>16</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" t="str">
-        <v>D</v>
-      </c>
-      <c r="F4">
-        <v>0.4</v>
-      </c>
-      <c r="G4" t="str">
-        <v>GRUPOS</v>
       </c>
       <c r="H4">
         <v>0.85</v>
@@ -7438,26 +7438,26 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="str">
+        <v>Tsukahara</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="str">
+        <v>D</v>
+      </c>
+      <c r="E5">
+        <v>0.4</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <v>13</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Tsukahara</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5" t="str">
-        <v>D</v>
-      </c>
-      <c r="F5">
-        <v>0.4</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
       </c>
       <c r="H5">
         <v>0.9</v>
@@ -7525,22 +7525,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
         <v>Doble giro atrás LC</v>
       </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
       <c r="C6">
-        <v>9</v>
-      </c>
-      <c r="D6">
         <v>4</v>
       </c>
-      <c r="E6" t="str">
+      <c r="D6" t="str">
         <v>C</v>
       </c>
-      <c r="F6">
+      <c r="E6">
         <v>0.3</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
         <v>Flic facial</v>
       </c>
+      <c r="B7">
+        <v>67</v>
+      </c>
       <c r="C7">
-        <v>67</v>
-      </c>
-      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" t="str">
-        <v>A</v>
-      </c>
-      <c r="F7">
+      <c r="D7" t="str">
+        <v>A</v>
+      </c>
+      <c r="E7">
         <v>0.1</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -7697,22 +7697,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
         <v>Salto del tigre</v>
       </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
       <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8" t="str">
-        <v>A</v>
-      </c>
-      <c r="F8">
+      <c r="D8" t="str">
+        <v>A</v>
+      </c>
+      <c r="E8">
         <v>0.1</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -7783,22 +7783,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
         <v>Doble en V atrás</v>
       </c>
+      <c r="B9">
+        <v>16</v>
+      </c>
       <c r="C9">
-        <v>16</v>
-      </c>
-      <c r="D9">
         <v>3</v>
       </c>
-      <c r="E9" t="str">
+      <c r="D9" t="str">
         <v>D</v>
       </c>
-      <c r="F9">
+      <c r="E9">
         <v>0.4</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -7869,25 +7869,25 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
-      </c>
-      <c r="B10" t="str">
         <v>Doble giro extendido adel LC</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-      <c r="E10" t="str">
+      <c r="D10" t="str">
         <v>D</v>
       </c>
-      <c r="F10">
+      <c r="E10">
         <v>0.4</v>
       </c>
+      <c r="F10" t="str">
+        <v>BPP</v>
+      </c>
       <c r="G10" t="str">
-        <v>BPP</v>
+        <v/>
       </c>
       <c r="H10">
         <v>0.9</v>
@@ -7955,22 +7955,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
         <v>Doble giro y medio atrás</v>
       </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
       <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" t="str">
+      <c r="D11" t="str">
         <v>D</v>
       </c>
-      <c r="F11">
+      <c r="E11">
         <v>0.4</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -8050,10 +8050,10 @@
         <v/>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>BPC</v>
       </c>
       <c r="E12" t="str">
-        <v>BPC</v>
+        <v/>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -8127,25 +8127,25 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>ARZONES</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>ALONSO</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>NOTA D</v>
+      </c>
+      <c r="G13" t="str">
         <v>NP</v>
-      </c>
-      <c r="B13" t="str">
-        <v>ARZONES</v>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v>ALONSO</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v>NOTA D</v>
       </c>
       <c r="H13" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -8212,26 +8212,26 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
+      <c r="A14" t="str">
+        <v>NOMBRE</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NÚM DE ID</v>
+      </c>
+      <c r="C14" t="str">
+        <v>GRUPO</v>
+      </c>
+      <c r="D14" t="str">
+        <v>VALOR</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Valor decimal</v>
+      </c>
+      <c r="F14">
+        <v>0.4</v>
+      </c>
+      <c r="G14">
         <v>11.6</v>
-      </c>
-      <c r="B14" t="str">
-        <v>NOMBRE</v>
-      </c>
-      <c r="C14" t="str">
-        <v>NÚM DE ID</v>
-      </c>
-      <c r="D14" t="str">
-        <v>GRUPO</v>
-      </c>
-      <c r="E14" t="str">
-        <v>VALOR</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Valor decimal</v>
-      </c>
-      <c r="G14">
-        <v>0.4</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -8299,25 +8299,25 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Probable NF</v>
-      </c>
-      <c r="B15" t="str">
         <v xml:space="preserve">Corte tijera </v>
+      </c>
+      <c r="B15">
+        <v>1</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="str">
-        <v>A</v>
-      </c>
-      <c r="F15">
+      <c r="D15" t="str">
+        <v>A</v>
+      </c>
+      <c r="E15">
         <v>0.1</v>
       </c>
+      <c r="F15" t="str">
+        <v>GRUPOS</v>
+      </c>
       <c r="G15" t="str">
-        <v>GRUPOS</v>
+        <v>Probable NF</v>
       </c>
       <c r="H15">
         <v>0.8</v>
@@ -8384,26 +8384,26 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
+      <c r="A16" t="str">
+        <v>Molino en arzones</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="str">
+        <v>A</v>
+      </c>
+      <c r="E16">
+        <v>0.1</v>
+      </c>
+      <c r="F16">
+        <v>1.2</v>
+      </c>
+      <c r="G16">
         <v>10.1</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Molino en arzones</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16" t="str">
-        <v>A</v>
-      </c>
-      <c r="F16">
-        <v>0.1</v>
-      </c>
-      <c r="G16">
-        <v>1.2</v>
       </c>
       <c r="H16">
         <v>0.7</v>
@@ -8471,19 +8471,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
-      </c>
-      <c r="B17" t="str">
         <v>Molino en arzones</v>
       </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
       <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
         <v>2</v>
       </c>
+      <c r="D17" t="str">
+        <v>A</v>
+      </c>
       <c r="E17" t="str">
-        <v>A</v>
+        <v/>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -8557,22 +8557,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
-      </c>
-      <c r="B18" t="str">
-        <v>Bajada lateral</v>
+        <v>Bajada lateral con 1/4 de giro</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" t="str">
-        <v>A</v>
-      </c>
-      <c r="F18">
+      <c r="D18" t="str">
+        <v>A</v>
+      </c>
+      <c r="E18">
         <v>0.1</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -8643,22 +8643,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
-      </c>
-      <c r="B19" t="str">
         <v>Molino</v>
       </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
       <c r="C19">
-        <v>7</v>
-      </c>
-      <c r="D19">
         <v>2</v>
       </c>
-      <c r="E19" t="str">
-        <v>A</v>
-      </c>
-      <c r="F19">
+      <c r="D19" t="str">
+        <v>A</v>
+      </c>
+      <c r="E19">
         <v>0.1</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -8729,19 +8729,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>1/4 de kher</v>
       </c>
       <c r="B20" t="str">
-        <v>1/4 de kher</v>
+        <v>EV</v>
       </c>
       <c r="C20" t="str">
-        <v>EV</v>
+        <v>X</v>
       </c>
       <c r="D20" t="str">
-        <v>X</v>
+        <v>A</v>
       </c>
       <c r="E20" t="str">
-        <v>A</v>
+        <v/>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -8815,25 +8815,25 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
-      </c>
-      <c r="B21" t="str">
         <v>1/4 Splindle</v>
       </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
       <c r="C21">
-        <v>25</v>
-      </c>
-      <c r="D21">
         <v>2</v>
       </c>
-      <c r="E21" t="str">
-        <v>A</v>
-      </c>
-      <c r="F21">
+      <c r="D21" t="str">
+        <v>A</v>
+      </c>
+      <c r="E21">
         <v>0.1</v>
       </c>
+      <c r="F21" t="str">
+        <v>BPP</v>
+      </c>
       <c r="G21" t="str">
-        <v>BPP</v>
+        <v/>
       </c>
       <c r="H21">
         <v>0.8</v>
@@ -8901,22 +8901,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
-      </c>
-      <c r="B22" t="str">
         <v>Finlandesa</v>
       </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
       <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
         <v>4</v>
       </c>
-      <c r="E22" t="str">
-        <v>A</v>
-      </c>
-      <c r="F22">
+      <c r="D22" t="str">
+        <v>A</v>
+      </c>
+      <c r="E22">
         <v>0.1</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -8987,25 +8987,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
+        <v>ANILLOS</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>ALONSO</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>NOTA D</v>
+      </c>
+      <c r="G23" t="str">
         <v>NP</v>
-      </c>
-      <c r="B23" t="str">
-        <v>ANILLOS</v>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <v>ALONSO</v>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v>NOTA D</v>
       </c>
       <c r="H23" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -9072,26 +9072,26 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>12.9</v>
+      <c r="A24" t="str">
+        <v>NOMBRE</v>
       </c>
       <c r="B24" t="str">
-        <v>NOMBRE</v>
+        <v>NÚM DE ID</v>
       </c>
       <c r="C24" t="str">
-        <v>NÚM DE ID</v>
+        <v>GRUPO</v>
       </c>
       <c r="D24" t="str">
-        <v>GRUPO</v>
+        <v>VALOR</v>
       </c>
       <c r="E24" t="str">
-        <v>VALOR</v>
-      </c>
-      <c r="F24" t="str">
         <v>Valor decimal</v>
       </c>
+      <c r="F24">
+        <v>1.6</v>
+      </c>
       <c r="G24">
-        <v>1.5</v>
+        <v>13</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -9159,25 +9159,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>Kip cristo</v>
+      </c>
+      <c r="B25">
+        <v>39</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="str">
+        <v>C</v>
+      </c>
+      <c r="E25">
+        <v>0.3</v>
+      </c>
+      <c r="F25" t="str">
+        <v>GRUPOS</v>
+      </c>
+      <c r="G25" t="str">
         <v>Probable NF</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Kip cristo</v>
-      </c>
-      <c r="C25">
-        <v>39</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25" t="str">
-        <v>C</v>
-      </c>
-      <c r="F25">
-        <v>0.3</v>
-      </c>
-      <c r="G25" t="str">
-        <v>GRUPOS</v>
       </c>
       <c r="H25">
         <v>0.65</v>
@@ -9244,26 +9244,26 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>11.4</v>
-      </c>
-      <c r="B26" t="str">
+      <c r="A26" t="str">
         <v>Plancha dorsal</v>
       </c>
+      <c r="B26">
+        <v>7</v>
+      </c>
       <c r="C26">
-        <v>7</v>
-      </c>
-      <c r="D26">
         <v>2</v>
       </c>
-      <c r="E26" t="str">
-        <v>A</v>
+      <c r="D26" t="str">
+        <v>A</v>
+      </c>
+      <c r="E26">
+        <v>0.1</v>
       </c>
       <c r="F26">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="G26">
-        <v>1.4</v>
+        <v>11.5</v>
       </c>
       <c r="H26">
         <v>0.9</v>
@@ -9331,22 +9331,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v/>
-      </c>
-      <c r="B27" t="str">
-        <v>Inlocada</v>
+        <v>Inglesa</v>
+      </c>
+      <c r="B27">
+        <v>31</v>
       </c>
       <c r="C27">
-        <v>37</v>
-      </c>
-      <c r="D27">
         <v>1</v>
       </c>
-      <c r="E27" t="str">
-        <v>A</v>
-      </c>
-      <c r="F27">
+      <c r="D27" t="str">
+        <v>A</v>
+      </c>
+      <c r="E27">
         <v>0.1</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -9417,22 +9417,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
-      </c>
-      <c r="B28" t="str">
-        <v>Inglesa</v>
+        <v>L sit</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>31</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="str">
-        <v>A</v>
-      </c>
-      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="str">
+        <v>A</v>
+      </c>
+      <c r="E28">
         <v>0.1</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
-      </c>
-      <c r="B29" t="str">
-        <v>L sit</v>
+        <v>Yamawaki</v>
+      </c>
+      <c r="B29">
+        <v>44</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29" t="str">
-        <v>A</v>
-      </c>
-      <c r="F29">
-        <v>0.1</v>
+      <c r="D29" t="str">
+        <v>B</v>
+      </c>
+      <c r="E29">
+        <v>0.2</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -9589,22 +9589,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
-      </c>
-      <c r="B30" t="str">
         <v>Kato 3"</v>
       </c>
+      <c r="B30">
+        <v>26</v>
+      </c>
       <c r="C30">
-        <v>26</v>
-      </c>
-      <c r="D30">
         <v>2</v>
       </c>
-      <c r="E30" t="str">
+      <c r="D30" t="str">
         <v>B</v>
       </c>
-      <c r="F30">
+      <c r="E30">
         <v>0.2</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -9675,25 +9675,25 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
-      </c>
-      <c r="B31" t="str">
         <v>Gigante sost</v>
       </c>
+      <c r="B31">
+        <v>75</v>
+      </c>
       <c r="C31">
-        <v>75</v>
-      </c>
-      <c r="D31">
         <v>1</v>
       </c>
-      <c r="E31" t="str">
+      <c r="D31" t="str">
         <v>C</v>
       </c>
-      <c r="F31">
+      <c r="E31">
         <v>0.3</v>
       </c>
+      <c r="F31" t="str">
+        <v>BPP</v>
+      </c>
       <c r="G31" t="str">
-        <v>BPP</v>
+        <v/>
       </c>
       <c r="H31">
         <v>0.75</v>
@@ -9761,22 +9761,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
-      </c>
-      <c r="B32" t="str">
         <v>Doble extendido atras</v>
       </c>
+      <c r="B32">
+        <v>33</v>
+      </c>
       <c r="C32">
-        <v>33</v>
-      </c>
-      <c r="D32">
         <v>4</v>
       </c>
-      <c r="E32" t="str">
+      <c r="D32" t="str">
         <v>C</v>
       </c>
-      <c r="F32">
+      <c r="E32">
         <v>0.3</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -9847,16 +9847,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v>SALTO DE CABALLO</v>
       </c>
       <c r="B33" t="str">
-        <v>SALTO DE CABALLO</v>
+        <v/>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>ALONSO</v>
       </c>
       <c r="D33" t="str">
-        <v>ALONSO</v>
+        <v/>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -9933,19 +9933,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>NOMBRE</v>
       </c>
       <c r="B34" t="str">
-        <v>NOMBRE</v>
+        <v>NÚM DE ID</v>
       </c>
       <c r="C34" t="str">
-        <v>NÚM DE ID</v>
+        <v>GRUPO</v>
       </c>
       <c r="D34" t="str">
-        <v>GRUPO</v>
+        <v>VALOR</v>
       </c>
       <c r="E34" t="str">
-        <v>VALOR</v>
+        <v/>
       </c>
       <c r="F34" t="str">
         <v/>
@@ -10019,25 +10019,25 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
+        <v>Tsukahara ext con 1 giro</v>
+      </c>
+      <c r="B35">
+        <v>125</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>3.6</v>
+      </c>
+      <c r="E35" t="str">
+        <v>NOTA D</v>
+      </c>
+      <c r="F35" t="str">
+        <v>SALTOS</v>
+      </c>
+      <c r="G35" t="str">
         <v>Probable NF</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Tsukahara ext con 1</v>
-      </c>
-      <c r="C35">
-        <v>125</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35">
-        <v>3.6</v>
-      </c>
-      <c r="F35" t="str">
-        <v>NOTA D</v>
-      </c>
-      <c r="G35" t="str">
-        <v>SALTOS</v>
       </c>
       <c r="H35">
         <v>0.65</v>
@@ -10104,26 +10104,26 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36">
+      <c r="A36" t="str">
+        <v>Tsukahara extendida</v>
+      </c>
+      <c r="B36">
+        <v>313</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36">
+        <v>2.8</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36">
+        <v>13.6</v>
+      </c>
+      <c r="G36">
         <v>12.299999999999999</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Tsukahara extendida</v>
-      </c>
-      <c r="C36">
-        <v>313</v>
-      </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-      <c r="E36">
-        <v>2.8</v>
-      </c>
-      <c r="F36" t="str">
-        <v/>
-      </c>
-      <c r="G36">
-        <v>13.6</v>
       </c>
       <c r="H36">
         <v>0.7</v>
@@ -10191,25 +10191,25 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
+        <v>PARALELAS</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>ALONSO</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>NOTA D</v>
+      </c>
+      <c r="G37" t="str">
         <v>NP</v>
-      </c>
-      <c r="B37" t="str">
-        <v>PARALELAS</v>
-      </c>
-      <c r="C37" t="str">
-        <v/>
-      </c>
-      <c r="D37" t="str">
-        <v>ALONSO</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-      <c r="F37" t="str">
-        <v/>
-      </c>
-      <c r="G37" t="str">
-        <v>NOTA D</v>
       </c>
       <c r="H37" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -10276,26 +10276,26 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
+      <c r="A38" t="str">
+        <v>NOMBRE</v>
+      </c>
+      <c r="B38" t="str">
+        <v>NÚM DE ID</v>
+      </c>
+      <c r="C38" t="str">
+        <v>GRUPO</v>
+      </c>
+      <c r="D38" t="str">
+        <v>VALOR</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Valor decimal</v>
+      </c>
+      <c r="F38">
+        <v>1.6</v>
+      </c>
+      <c r="G38">
         <v>13</v>
-      </c>
-      <c r="B38" t="str">
-        <v>NOMBRE</v>
-      </c>
-      <c r="C38" t="str">
-        <v>NÚM DE ID</v>
-      </c>
-      <c r="D38" t="str">
-        <v>GRUPO</v>
-      </c>
-      <c r="E38" t="str">
-        <v>VALOR</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Valor decimal</v>
-      </c>
-      <c r="G38">
-        <v>1.6</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -10363,25 +10363,25 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
+        <v xml:space="preserve">Alemana </v>
+      </c>
+      <c r="B39">
+        <v>73</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="str">
+        <v>A</v>
+      </c>
+      <c r="E39">
+        <v>0.1</v>
+      </c>
+      <c r="F39" t="str">
+        <v>GRUPOS</v>
+      </c>
+      <c r="G39" t="str">
         <v>Probable NF</v>
-      </c>
-      <c r="B39" t="str">
-        <v xml:space="preserve">Alemana </v>
-      </c>
-      <c r="C39">
-        <v>73</v>
-      </c>
-      <c r="D39">
-        <v>3</v>
-      </c>
-      <c r="E39" t="str">
-        <v>A</v>
-      </c>
-      <c r="F39">
-        <v>0.1</v>
-      </c>
-      <c r="G39" t="str">
-        <v>GRUPOS</v>
       </c>
       <c r="H39">
         <v>0.9</v>
@@ -10448,26 +10448,26 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
+      <c r="A40" t="str">
+        <v>Kato</v>
+      </c>
+      <c r="B40">
+        <v>8</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40" t="str">
+        <v>B</v>
+      </c>
+      <c r="E40">
+        <v>0.2</v>
+      </c>
+      <c r="F40">
+        <v>1.4</v>
+      </c>
+      <c r="G40">
         <v>11.5</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Kato</v>
-      </c>
-      <c r="C40">
-        <v>8</v>
-      </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="E40" t="str">
-        <v>B</v>
-      </c>
-      <c r="F40">
-        <v>0.2</v>
-      </c>
-      <c r="G40">
-        <v>1.4</v>
       </c>
       <c r="H40">
         <v>0.85</v>
@@ -10535,22 +10535,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v/>
-      </c>
-      <c r="B41" t="str">
         <v>Moy extendido</v>
       </c>
+      <c r="B41">
+        <v>15</v>
+      </c>
       <c r="C41">
-        <v>15</v>
-      </c>
-      <c r="D41">
         <v>3</v>
       </c>
-      <c r="E41" t="str">
+      <c r="D41" t="str">
         <v>C</v>
       </c>
-      <c r="F41">
+      <c r="E41">
         <v>0.3</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -10621,22 +10621,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v/>
-      </c>
-      <c r="B42" t="str">
         <v>Cambio</v>
       </c>
+      <c r="B42">
+        <v>91</v>
+      </c>
       <c r="C42">
-        <v>91</v>
-      </c>
-      <c r="D42">
         <v>2</v>
       </c>
-      <c r="E42" t="str">
-        <v>A</v>
-      </c>
-      <c r="F42">
+      <c r="D42" t="str">
+        <v>A</v>
+      </c>
+      <c r="E42">
         <v>0.1</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -10707,22 +10707,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
-      </c>
-      <c r="B43" t="str">
         <v>Kenmotsu</v>
       </c>
+      <c r="B43">
+        <v>21</v>
+      </c>
       <c r="C43">
-        <v>21</v>
-      </c>
-      <c r="D43">
         <v>3</v>
       </c>
-      <c r="E43" t="str">
+      <c r="D43" t="str">
         <v>C</v>
       </c>
-      <c r="F43">
+      <c r="E43">
         <v>0.3</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -10793,22 +10793,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
-      </c>
-      <c r="B44" t="str">
         <v>Felge</v>
       </c>
+      <c r="B44">
+        <v>116</v>
+      </c>
       <c r="C44">
-        <v>116</v>
-      </c>
-      <c r="D44">
         <v>3</v>
       </c>
-      <c r="E44" t="str">
+      <c r="D44" t="str">
         <v>B</v>
       </c>
-      <c r="F44">
+      <c r="E44">
         <v>0.2</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -10879,25 +10879,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v/>
-      </c>
-      <c r="B45" t="str">
         <v xml:space="preserve">Braq Subida de pecho </v>
+      </c>
+      <c r="B45">
+        <v>1</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" t="str">
-        <v>A</v>
-      </c>
-      <c r="F45">
+      <c r="D45" t="str">
+        <v>A</v>
+      </c>
+      <c r="E45">
         <v>0.1</v>
       </c>
+      <c r="F45" t="str">
+        <v>BPP</v>
+      </c>
       <c r="G45" t="str">
-        <v>BPP</v>
+        <v/>
       </c>
       <c r="H45">
         <v>0.8</v>
@@ -10965,22 +10965,22 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
-      </c>
-      <c r="B46" t="str">
         <v>Doble mortal agrup atrás</v>
       </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
       <c r="C46">
-        <v>45</v>
-      </c>
-      <c r="D46">
         <v>4</v>
       </c>
-      <c r="E46" t="str">
+      <c r="D46" t="str">
         <v>C</v>
       </c>
-      <c r="F46">
+      <c r="E46">
         <v>0.3</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -11051,25 +11051,25 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
+        <v>FIJA</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v>ALONSO</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>NOTA D</v>
+      </c>
+      <c r="G47" t="str">
         <v>NP</v>
-      </c>
-      <c r="B47" t="str">
-        <v>FIJA</v>
-      </c>
-      <c r="C47" t="str">
-        <v/>
-      </c>
-      <c r="D47" t="str">
-        <v>ALONSO</v>
-      </c>
-      <c r="E47" t="str">
-        <v/>
-      </c>
-      <c r="F47" t="str">
-        <v/>
-      </c>
-      <c r="G47" t="str">
-        <v>NOTA D</v>
       </c>
       <c r="H47" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -11136,26 +11136,26 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48">
+      <c r="A48" t="str">
+        <v>NOMBRE</v>
+      </c>
+      <c r="B48" t="str">
+        <v>NÚM DE ID</v>
+      </c>
+      <c r="C48" t="str">
+        <v>GRUPO</v>
+      </c>
+      <c r="D48" t="str">
+        <v>VALOR</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Valor decimal</v>
+      </c>
+      <c r="F48">
+        <v>1.5</v>
+      </c>
+      <c r="G48">
         <v>13.2</v>
-      </c>
-      <c r="B48" t="str">
-        <v>NOMBRE</v>
-      </c>
-      <c r="C48" t="str">
-        <v>NÚM DE ID</v>
-      </c>
-      <c r="D48" t="str">
-        <v>GRUPO</v>
-      </c>
-      <c r="E48" t="str">
-        <v>VALOR</v>
-      </c>
-      <c r="F48" t="str">
-        <v>Valor decimal</v>
-      </c>
-      <c r="G48">
-        <v>1.5</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -11223,25 +11223,25 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
+        <v>Gienger</v>
+      </c>
+      <c r="B49">
+        <v>58</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49" t="str">
+        <v>D</v>
+      </c>
+      <c r="E49">
+        <v>0.4</v>
+      </c>
+      <c r="F49" t="str">
+        <v>GRUPOS</v>
+      </c>
+      <c r="G49" t="str">
         <v>Probable NF</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Gienger</v>
-      </c>
-      <c r="C49">
-        <v>58</v>
-      </c>
-      <c r="D49">
-        <v>2</v>
-      </c>
-      <c r="E49" t="str">
-        <v>D</v>
-      </c>
-      <c r="F49">
-        <v>0.4</v>
-      </c>
-      <c r="G49" t="str">
-        <v>GRUPOS</v>
       </c>
       <c r="H49">
         <v>0.85</v>
@@ -11308,26 +11308,26 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50">
+      <c r="A50" t="str">
+        <v>Alemana</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="D50" t="str">
+        <v>A</v>
+      </c>
+      <c r="E50">
+        <v>0.1</v>
+      </c>
+      <c r="F50">
+        <v>1.7</v>
+      </c>
+      <c r="G50">
         <v>11.7</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Alemana</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>3</v>
-      </c>
-      <c r="E50" t="str">
-        <v>A</v>
-      </c>
-      <c r="F50">
-        <v>0.1</v>
-      </c>
-      <c r="G50">
-        <v>1.7</v>
       </c>
       <c r="H50">
         <v>0.85</v>
@@ -11395,22 +11395,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v/>
-      </c>
-      <c r="B51" t="str">
         <v>Molino</v>
       </c>
+      <c r="B51">
+        <v>13</v>
+      </c>
       <c r="C51">
-        <v>13</v>
-      </c>
-      <c r="D51">
         <v>1</v>
       </c>
-      <c r="E51" t="str">
-        <v>A</v>
-      </c>
-      <c r="F51">
+      <c r="D51" t="str">
+        <v>A</v>
+      </c>
+      <c r="E51">
         <v>0.1</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -11481,22 +11481,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v>Cambio sencillo</v>
       </c>
       <c r="B52" t="str">
-        <v>Cambio sencillo</v>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52">
+        <v/>
+      </c>
+      <c r="C52">
         <v>1</v>
       </c>
-      <c r="E52" t="str">
-        <v>A</v>
-      </c>
-      <c r="F52">
+      <c r="D52" t="str">
+        <v>A</v>
+      </c>
+      <c r="E52">
         <v>0.1</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -11567,22 +11567,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
-      </c>
-      <c r="B53" t="str">
         <v>Gigante</v>
       </c>
+      <c r="B53">
+        <v>31</v>
+      </c>
       <c r="C53">
-        <v>31</v>
-      </c>
-      <c r="D53">
         <v>1</v>
       </c>
-      <c r="E53" t="str">
-        <v>A</v>
-      </c>
-      <c r="F53">
+      <c r="D53" t="str">
+        <v>A</v>
+      </c>
+      <c r="E53">
         <v>0.1</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -11653,22 +11653,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
-      </c>
-      <c r="B54" t="str">
         <v>Salvada</v>
       </c>
+      <c r="B54">
+        <v>25</v>
+      </c>
       <c r="C54">
-        <v>25</v>
-      </c>
-      <c r="D54">
         <v>3</v>
       </c>
-      <c r="E54" t="str">
-        <v>A</v>
-      </c>
-      <c r="F54">
+      <c r="D54" t="str">
+        <v>A</v>
+      </c>
+      <c r="E54">
         <v>0.1</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -11739,25 +11739,25 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
-      </c>
-      <c r="B55" t="str">
         <v>Gigante Saltado</v>
       </c>
+      <c r="B55">
+        <v>44</v>
+      </c>
       <c r="C55">
-        <v>44</v>
-      </c>
-      <c r="D55">
         <v>1</v>
       </c>
-      <c r="E55" t="str">
+      <c r="D55" t="str">
         <v>B</v>
       </c>
-      <c r="F55">
+      <c r="E55">
         <v>0.2</v>
       </c>
+      <c r="F55" t="str">
+        <v>BPP</v>
+      </c>
       <c r="G55" t="str">
-        <v>BPP</v>
+        <v/>
       </c>
       <c r="H55">
         <v>0.01</v>
@@ -11825,22 +11825,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
-      </c>
-      <c r="B56" t="str">
         <v>Multiple extendido atras</v>
       </c>
+      <c r="B56">
+        <v>41</v>
+      </c>
       <c r="C56">
-        <v>41</v>
-      </c>
-      <c r="D56">
         <v>4</v>
       </c>
-      <c r="E56" t="str">
+      <c r="D56" t="str">
         <v>D</v>
       </c>
-      <c r="F56">
+      <c r="E56">
         <v>0.4</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -11920,10 +11920,10 @@
         <v/>
       </c>
       <c r="D57" t="str">
-        <v/>
+        <v>BPC</v>
       </c>
       <c r="E57" t="str">
-        <v>BPC</v>
+        <v/>
       </c>
       <c r="F57" t="str">
         <v/>
@@ -16474,7 +16474,7 @@
         <v>Doble en c atrás</v>
       </c>
       <c r="L2" t="str">
-        <v>Doble en V atrás</v>
+        <v>Doble adelante en c</v>
       </c>
       <c r="M2" t="str">
         <v>Doble adelante en c</v>
@@ -16524,7 +16524,7 @@
         <v>Doble giro y medio atras</v>
       </c>
       <c r="L3" t="str">
-        <v>Doble adelante en c</v>
+        <v>Doble en V atrás</v>
       </c>
       <c r="M3" t="str">
         <v>Tsukahara</v>
@@ -16574,7 +16574,7 @@
         <v>Varani LC</v>
       </c>
       <c r="L4" t="str">
-        <v>Giro al frente extendido LC</v>
+        <v>Flick Flack LC</v>
       </c>
       <c r="M4" t="str">
         <v>Doble giro atrás LC</v>
@@ -16618,13 +16618,13 @@
         <v>Tempo</v>
       </c>
       <c r="J5" t="str">
-        <v>Circulo en suelo</v>
+        <v>Arabesca</v>
       </c>
       <c r="K5" t="str">
         <v>Rusa 2"</v>
       </c>
       <c r="L5" t="str">
-        <v>Arabesca</v>
+        <v>Giro atrás LC</v>
       </c>
       <c r="M5" t="str">
         <v>Flic facial</v>
@@ -16662,19 +16662,19 @@
         <v>Arabesca</v>
       </c>
       <c r="H6" t="str">
-        <v>Arabesca</v>
+        <v>Flic facial</v>
       </c>
       <c r="I6" t="str">
         <v>Giro ext atrás</v>
       </c>
       <c r="J6" t="str">
+        <v>Giro al frente extendido</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Giro y medio ad ext</v>
+      </c>
+      <c r="L6" t="str">
         <v>Arabesca</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Arabesca</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Doble en c atrás</v>
       </c>
       <c r="M6" t="str">
         <v>Salto del tigre</v>
@@ -16712,19 +16712,19 @@
         <v>Flic facial</v>
       </c>
       <c r="H7" t="str">
-        <v>Giro al frente extendido</v>
+        <v>Arabesca</v>
       </c>
       <c r="I7" t="str">
         <v>Arabesca</v>
       </c>
       <c r="J7" t="str">
-        <v>Giro ext atrás</v>
+        <v>Giro ext atrás LC</v>
       </c>
       <c r="K7" t="str">
-        <v>Doble giro atras</v>
+        <v>Doble giro atrás LC</v>
       </c>
       <c r="L7" t="str">
-        <v>Giro atrás LC</v>
+        <v>Giro al frente ext</v>
       </c>
       <c r="M7" t="str">
         <v>Doble en V atrás</v>
@@ -16774,7 +16774,7 @@
         <v>Flick Flack</v>
       </c>
       <c r="L8" t="str">
-        <v>Flick Flack</v>
+        <v>Mortal Ext ade</v>
       </c>
       <c r="M8" t="str">
         <v>Doble giro extendido adel LC</v>
@@ -16824,7 +16824,7 @@
         <v>Mortal Ext atrás</v>
       </c>
       <c r="L9" t="str">
-        <v>Mortal Ext atrás</v>
+        <v>Doble en c atrás</v>
       </c>
       <c r="M9" t="str">
         <v>Doble giro y medio atrás</v>
@@ -16947,7 +16947,7 @@
         <v>Molino en arzones</v>
       </c>
       <c r="C12" t="str">
-        <v>1/2 Splindle</v>
+        <v>Molino transversal</v>
       </c>
       <c r="D12" t="str">
         <v>Sivado</v>
@@ -16997,10 +16997,10 @@
         <v>Bajada lateral</v>
       </c>
       <c r="C13" t="str">
-        <v>Thomas</v>
+        <v>1/2 Splindle</v>
       </c>
       <c r="D13" t="str">
-        <v>1/2 Magyar</v>
+        <v>Checa dorsal</v>
       </c>
       <c r="E13" t="str">
         <v>1/2 Magyar</v>
@@ -17027,7 +17027,7 @@
         <v>Molino transversal</v>
       </c>
       <c r="M13" t="str">
-        <v>Bajada lateral</v>
+        <v>Bajada lateral con 1/4 de giro</v>
       </c>
       <c r="N13" t="str">
         <v>Magyar en punta (splindle)</v>
@@ -17047,10 +17047,10 @@
         <v>Molino</v>
       </c>
       <c r="C14" t="str">
-        <v>Checa dorsal</v>
+        <v>Thomas</v>
       </c>
       <c r="D14" t="str">
-        <v>1/2 Sivado</v>
+        <v xml:space="preserve">Stockli </v>
       </c>
       <c r="E14" t="str">
         <v>1/2 Sivado</v>
@@ -17097,10 +17097,10 @@
         <v>1/4 de kher</v>
       </c>
       <c r="C15" t="str">
-        <v>1/4 Splindle</v>
+        <v>Checa dorsal</v>
       </c>
       <c r="D15" t="str">
-        <v>Checa dorsal</v>
+        <v>1/2 Magyar</v>
       </c>
       <c r="E15" t="str">
         <v>Checa dorsal</v>
@@ -17147,10 +17147,10 @@
         <v>1/4 splindle</v>
       </c>
       <c r="C16" t="str">
-        <v>Molino Lateral</v>
+        <v xml:space="preserve">Stockli </v>
       </c>
       <c r="D16" t="str">
-        <v>1/2 Splindle</v>
+        <v>1/2 Sivado</v>
       </c>
       <c r="E16" t="str">
         <v>1/2 Splindle</v>
@@ -17221,7 +17221,7 @@
         <v>Finlandesa</v>
       </c>
       <c r="K17" t="str">
-        <v>Finlandesa</v>
+        <v>Triple rusa a Flank</v>
       </c>
       <c r="L17" t="str">
         <v>Finlandesa</v>
@@ -17377,7 +17377,7 @@
         <v>Kato 3"</v>
       </c>
       <c r="M20" t="str">
-        <v>Inlocada</v>
+        <v>Inglesa</v>
       </c>
       <c r="N20" t="str">
         <v>Cristo</v>
@@ -17421,13 +17421,13 @@
         <v>L sit</v>
       </c>
       <c r="K21" t="str">
-        <v>Inglesa</v>
+        <v>Dominada adelante a Lsit</v>
       </c>
       <c r="L21" t="str">
         <v>Gigante Pas</v>
       </c>
       <c r="M21" t="str">
-        <v>Inglesa</v>
+        <v>L sit</v>
       </c>
       <c r="N21" t="str">
         <v>Inglesa</v>
@@ -17477,7 +17477,7 @@
         <v>Gigante sost</v>
       </c>
       <c r="M22" t="str">
-        <v>L sit</v>
+        <v>Yamawaki</v>
       </c>
       <c r="N22" t="str">
         <v>L sit</v>
@@ -17650,7 +17650,7 @@
         <v>Tsukahara en C</v>
       </c>
       <c r="D26" t="str">
-        <v>Tsukahara en C</v>
+        <v>Tsukahara en carpa</v>
       </c>
       <c r="E26" t="str">
         <v>Tsukahara en C</v>
@@ -17668,7 +17668,7 @@
         <v>Tsukahara ext</v>
       </c>
       <c r="J26" t="str">
-        <v>Tsukahara en carpa</v>
+        <v>Tsukahara ext</v>
       </c>
       <c r="K26" t="str">
         <v>Tsukahara ext</v>
@@ -17677,7 +17677,7 @@
         <v>Tsukahara ext con giro</v>
       </c>
       <c r="M26" t="str">
-        <v>Tsukahara ext con 1</v>
+        <v>Tsukahara ext con 1 giro</v>
       </c>
       <c r="N26" t="str">
         <v>Tsukahara ext con 1 giro</v>
@@ -18321,7 +18321,7 @@
         <v>Endo</v>
       </c>
       <c r="K39" t="str">
-        <v>Molino</v>
+        <v>Gigante</v>
       </c>
       <c r="L39" t="str">
         <v>Gigante</v>
@@ -18368,10 +18368,10 @@
         <v>Cambio directo</v>
       </c>
       <c r="J40" t="str">
-        <v>Cambio sencillo</v>
+        <v>Endo cerrado</v>
       </c>
       <c r="K40" t="str">
-        <v>Endo</v>
+        <v>Cambio directo</v>
       </c>
       <c r="L40" t="str">
         <v>Cambio directo</v>
@@ -18421,7 +18421,7 @@
         <v>Gigante</v>
       </c>
       <c r="K41" t="str">
-        <v>Cambio sencillo</v>
+        <v>Molino</v>
       </c>
       <c r="L41" t="str">
         <v>Molino</v>
@@ -18471,7 +18471,7 @@
         <v>Salvada</v>
       </c>
       <c r="K42" t="str">
-        <v>Gigante</v>
+        <v>Endo</v>
       </c>
       <c r="L42" t="str">
         <v>Cambio sencillo</v>
@@ -19245,7 +19245,7 @@
         <v>11.6</v>
       </c>
       <c r="D4">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="E4">
         <v>13.6</v>
@@ -19257,7 +19257,7 @@
         <v>13.2</v>
       </c>
       <c r="H4">
-        <v>70</v>
+        <v>70.1</v>
       </c>
     </row>
     <row r="5">
@@ -19291,13 +19291,13 @@
         <v>CHAMPI</v>
       </c>
       <c r="B6">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="C6">
-        <v>12.9</v>
+        <v>13.299999999999999</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="E6">
         <v>12.8</v>
@@ -19309,7 +19309,7 @@
         <v>13.2</v>
       </c>
       <c r="H6">
-        <v>69.39999999999999</v>
+        <v>70.1</v>
       </c>
     </row>
     <row r="7">
@@ -19317,7 +19317,7 @@
         <v>ISAAC</v>
       </c>
       <c r="B7">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="C7">
         <v>12.700000000000001</v>
@@ -19326,16 +19326,16 @@
         <v>13</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="F7">
         <v>12.700000000000001</v>
       </c>
       <c r="G7">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="8">
@@ -19346,7 +19346,7 @@
         <v>13.200000000000001</v>
       </c>
       <c r="C8">
-        <v>12.2</v>
+        <v>11.799999999999999</v>
       </c>
       <c r="D8">
         <v>12.8</v>
@@ -19361,7 +19361,7 @@
         <v>13.1</v>
       </c>
       <c r="H8">
-        <v>68.8</v>
+        <v>68.39999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -19369,7 +19369,7 @@
         <v>FER</v>
       </c>
       <c r="B9">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="C9">
         <v>12.2</v>
@@ -19387,7 +19387,7 @@
         <v>12</v>
       </c>
       <c r="H9">
-        <v>67.69999999999999</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="10">
@@ -19413,7 +19413,7 @@
         <v>12.4</v>
       </c>
       <c r="H10">
-        <v>67.8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -19424,7 +19424,7 @@
         <v>13.1</v>
       </c>
       <c r="C11">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="D11">
         <v>12.5</v>
@@ -19439,7 +19439,7 @@
         <v>11.799999999999999</v>
       </c>
       <c r="H11">
-        <v>66.39999999999999</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="12">
@@ -19456,7 +19456,7 @@
         <v>12.7</v>
       </c>
       <c r="E12">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="F12">
         <v>12.5</v>
@@ -19465,7 +19465,7 @@
         <v>11.9</v>
       </c>
       <c r="H12">
-        <v>67.39999999999999</v>
+        <v>67.6</v>
       </c>
     </row>
     <row r="13">
@@ -19637,7 +19637,7 @@
         <v>0.4</v>
       </c>
       <c r="D4">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E4">
         <v>3.6</v>
@@ -19654,7 +19654,7 @@
         <v>MIKEL</v>
       </c>
       <c r="B5">
-        <v>2.0000000000000004</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>0.9</v>
@@ -19677,13 +19677,13 @@
         <v>CHAMPI</v>
       </c>
       <c r="B6">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D6">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="E6">
         <v>2.8</v>
@@ -19700,7 +19700,7 @@
         <v>ISAAC</v>
       </c>
       <c r="B7">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="C7">
         <v>1.3</v>
@@ -19709,13 +19709,13 @@
         <v>1.7</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="F7">
         <v>1.4000000000000001</v>
       </c>
       <c r="G7">
-        <v>1.3</v>
+        <v>1.5000000000000002</v>
       </c>
     </row>
     <row r="8">
@@ -19746,7 +19746,7 @@
         <v>FER</v>
       </c>
       <c r="B9">
-        <v>1.2</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="C9">
         <v>0.9999999999999999</v>
@@ -19795,7 +19795,7 @@
         <v>1.0999999999999999</v>
       </c>
       <c r="C11">
-        <v>1.3000000000000003</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D11">
         <v>0.8999999999999999</v>
@@ -19824,7 +19824,7 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="F12">
         <v>0.8999999999999999</v>
@@ -20036,7 +20036,7 @@
         <v>1.6</v>
       </c>
       <c r="C6">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="D6">
         <v>1.4</v>
@@ -20082,7 +20082,7 @@
         <v>1.4</v>
       </c>
       <c r="C8">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="D8">
         <v>1.3</v>
@@ -20286,13 +20286,13 @@
         <v>AA NP</v>
       </c>
       <c r="F1" t="str">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="G1" t="str">
         <v>AA</v>
       </c>
       <c r="H1" t="str">
-        <v>66.4</v>
+        <v>66.5</v>
       </c>
       <c r="I1" t="str">
         <v>77.07%</v>
@@ -20925,10 +20925,10 @@
         <v>REQUISITO</v>
       </c>
       <c r="G13">
-        <v>1.3000000000000003</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="H13">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -21034,7 +21034,7 @@
         <v>1.6</v>
       </c>
       <c r="H15">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="I15">
         <v>0.85</v>
@@ -21066,19 +21066,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1/2 Splindle</v>
+        <v>Molino transversal</v>
       </c>
       <c r="B16">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E16">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F16" t="str">
         <v>II</v>
@@ -21119,22 +21119,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Thomas</v>
-      </c>
-      <c r="B17" t="str">
-        <v>EV</v>
+        <v>1/2 Splindle</v>
+      </c>
+      <c r="B17">
+        <v>26</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E17">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="str">
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -21172,22 +21172,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Checa dorsal</v>
-      </c>
-      <c r="B18">
-        <v>74</v>
+        <v>Thomas</v>
+      </c>
+      <c r="B18" t="str">
+        <v>EV</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E18">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F18" t="str">
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -21225,19 +21225,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1/4 Splindle</v>
+        <v>Checa dorsal</v>
       </c>
       <c r="B19">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E19">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="str">
         <v>II</v>
@@ -21278,19 +21278,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Molino Lateral</v>
+        <v xml:space="preserve">Stockli </v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E20">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F20" t="str">
         <v>II</v>
@@ -24372,10 +24372,10 @@
         <v>PISO</v>
       </c>
       <c r="C48" t="str">
-        <v>Arabesca</v>
+        <v>Flic facial</v>
       </c>
       <c r="D48">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -24398,19 +24398,19 @@
         <v>PISO</v>
       </c>
       <c r="C49" t="str">
-        <v>Giro al frente extendido</v>
+        <v>Arabesca</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G49">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -26530,10 +26530,10 @@
         <v>PISO</v>
       </c>
       <c r="C131" t="str">
-        <v>Circulo en suelo</v>
+        <v>Arabesca</v>
       </c>
       <c r="D131">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -26556,19 +26556,19 @@
         <v>PISO</v>
       </c>
       <c r="C132" t="str">
-        <v>Arabesca</v>
+        <v>Giro al frente extendido</v>
       </c>
       <c r="D132">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F132" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="G132">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H132" t="str">
         <v/>
@@ -26582,7 +26582,7 @@
         <v>PISO</v>
       </c>
       <c r="C133" t="str">
-        <v>Giro ext atrás</v>
+        <v>Giro ext atrás LC</v>
       </c>
       <c r="D133">
         <v>9</v>
@@ -27076,16 +27076,16 @@
         <v>SALTO</v>
       </c>
       <c r="C152" t="str">
-        <v>Tsukahara en carpa</v>
+        <v>Tsukahara ext</v>
       </c>
       <c r="D152">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E152">
         <v>3</v>
       </c>
       <c r="F152">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -27440,19 +27440,19 @@
         <v>FIJA</v>
       </c>
       <c r="C166" t="str">
-        <v>Cambio sencillo</v>
+        <v>Endo cerrado</v>
       </c>
       <c r="D166">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F166" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="G166">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H166" t="str">
         <v/>
@@ -27648,19 +27648,19 @@
         <v>PISO</v>
       </c>
       <c r="C174" t="str">
-        <v>Arabesca</v>
+        <v>Giro y medio ad ext</v>
       </c>
       <c r="D174">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="E174">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F174" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="G174">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H174" t="str">
         <v/>
@@ -27674,7 +27674,7 @@
         <v>PISO</v>
       </c>
       <c r="C175" t="str">
-        <v>Doble giro atras</v>
+        <v>Doble giro atrás LC</v>
       </c>
       <c r="D175">
         <v>9</v>
@@ -27934,19 +27934,19 @@
         <v>ARZON</v>
       </c>
       <c r="C185" t="str">
-        <v>Finlandesa</v>
+        <v>Triple rusa a Flank</v>
       </c>
       <c r="D185">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E185">
         <v>4</v>
       </c>
       <c r="F185" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="G185">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H185" t="str">
         <v/>
@@ -28038,19 +28038,19 @@
         <v>ANILLOS</v>
       </c>
       <c r="C189" t="str">
-        <v>Inglesa</v>
+        <v>Dominada adelante a Lsit</v>
       </c>
       <c r="D189">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E189">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F189" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G189">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H189" t="str">
         <v/>
@@ -28506,7 +28506,7 @@
         <v>FIJA</v>
       </c>
       <c r="C207" t="str">
-        <v>Molino</v>
+        <v>Gigante</v>
       </c>
       <c r="D207">
         <v>13</v>
@@ -28532,19 +28532,19 @@
         <v>FIJA</v>
       </c>
       <c r="C208" t="str">
-        <v>Endo</v>
+        <v>Cambio directo</v>
       </c>
       <c r="D208">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E208">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F208" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G208">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H208" t="str">
         <v/>
@@ -28558,10 +28558,10 @@
         <v>FIJA</v>
       </c>
       <c r="C209" t="str">
-        <v>Cambio sencillo</v>
+        <v>Molino</v>
       </c>
       <c r="D209">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E209">
         <v>1</v>
@@ -28584,19 +28584,19 @@
         <v>FIJA</v>
       </c>
       <c r="C210" t="str">
-        <v>Gigante</v>
+        <v>Endo</v>
       </c>
       <c r="D210">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E210">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F210" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G210">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H210" t="str">
         <v/>
@@ -28636,13 +28636,13 @@
         <v>PISO</v>
       </c>
       <c r="C212" t="str">
-        <v>Doble en V atrás</v>
+        <v>Doble adelante en c</v>
       </c>
       <c r="D212">
         <v>16</v>
       </c>
       <c r="E212">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F212" t="str">
         <v>D</v>
@@ -28662,13 +28662,13 @@
         <v>PISO</v>
       </c>
       <c r="C213" t="str">
-        <v>Doble adelante en c</v>
+        <v>Doble en V atrás</v>
       </c>
       <c r="D213">
         <v>16</v>
       </c>
       <c r="E213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F213" t="str">
         <v>D</v>
@@ -28688,19 +28688,19 @@
         <v>PISO</v>
       </c>
       <c r="C214" t="str">
-        <v>Giro al frente extendido LC</v>
+        <v>Flick Flack LC</v>
       </c>
       <c r="D214">
+        <v>13</v>
+      </c>
+      <c r="E214">
         <v>3</v>
       </c>
-      <c r="E214">
-        <v>4</v>
-      </c>
       <c r="F214" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G214">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H214" t="str">
         <v/>
@@ -28714,19 +28714,19 @@
         <v>PISO</v>
       </c>
       <c r="C215" t="str">
-        <v>Arabesca</v>
+        <v>Giro atrás LC</v>
       </c>
       <c r="D215">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="E215">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F215" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G215">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H215" t="str">
         <v/>
@@ -28740,19 +28740,19 @@
         <v>PISO</v>
       </c>
       <c r="C216" t="str">
-        <v>Doble en c atrás</v>
+        <v>Arabesca</v>
       </c>
       <c r="D216">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="E216">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F216" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G216">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H216" t="str">
         <v/>
@@ -28766,19 +28766,19 @@
         <v>PISO</v>
       </c>
       <c r="C217" t="str">
-        <v>Giro atrás LC</v>
+        <v>Giro al frente ext</v>
       </c>
       <c r="D217">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E217">
         <v>4</v>
       </c>
       <c r="F217" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="G217">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H217" t="str">
         <v/>
@@ -28792,19 +28792,19 @@
         <v>PISO</v>
       </c>
       <c r="C218" t="str">
-        <v>Flick Flack</v>
+        <v>Mortal Ext ade</v>
       </c>
       <c r="D218">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E218">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F218" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G218">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H218" t="str">
         <v/>
@@ -28818,19 +28818,19 @@
         <v>PISO</v>
       </c>
       <c r="C219" t="str">
-        <v>Mortal Ext atrás</v>
+        <v>Doble en c atrás</v>
       </c>
       <c r="D219">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E219">
         <v>3</v>
       </c>
       <c r="F219" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="G219">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H219" t="str">
         <v/>
@@ -30014,7 +30014,7 @@
         <v>ARZON</v>
       </c>
       <c r="C265" t="str">
-        <v>Bajada lateral</v>
+        <v>Bajada lateral con 1/4 de giro</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -30196,10 +30196,10 @@
         <v>ANILLOS</v>
       </c>
       <c r="C272" t="str">
-        <v>Inlocada</v>
+        <v>Inglesa</v>
       </c>
       <c r="D272">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E272">
         <v>1</v>
@@ -30222,13 +30222,13 @@
         <v>ANILLOS</v>
       </c>
       <c r="C273" t="str">
-        <v>Inglesa</v>
+        <v>L sit</v>
       </c>
       <c r="D273">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E273">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F273" t="str">
         <v>A</v>
@@ -30248,19 +30248,19 @@
         <v>ANILLOS</v>
       </c>
       <c r="C274" t="str">
-        <v>L sit</v>
+        <v>Yamawaki</v>
       </c>
       <c r="D274">
+        <v>44</v>
+      </c>
+      <c r="E274">
         <v>1</v>
       </c>
-      <c r="E274">
-        <v>2</v>
-      </c>
       <c r="F274" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G274">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H274" t="str">
         <v/>
@@ -30352,7 +30352,7 @@
         <v>SALTO</v>
       </c>
       <c r="C278" t="str">
-        <v>Tsukahara ext con 1</v>
+        <v>Tsukahara ext con 1 giro</v>
       </c>
       <c r="D278">
         <v>125</v>
@@ -33264,19 +33264,19 @@
         <v>ARZON</v>
       </c>
       <c r="C390" t="str">
-        <v>1/2 Splindle</v>
+        <v>Molino transversal</v>
       </c>
       <c r="D390">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E390">
         <v>2</v>
       </c>
       <c r="F390" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G390">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H390" t="str">
         <v/>
@@ -33290,19 +33290,19 @@
         <v>ARZON</v>
       </c>
       <c r="C391" t="str">
-        <v>Thomas</v>
-      </c>
-      <c r="D391" t="str">
-        <v>EV</v>
+        <v>1/2 Splindle</v>
+      </c>
+      <c r="D391">
+        <v>26</v>
       </c>
       <c r="E391">
         <v>2</v>
       </c>
       <c r="F391" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G391">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H391" t="str">
         <v/>
@@ -33316,19 +33316,19 @@
         <v>ARZON</v>
       </c>
       <c r="C392" t="str">
-        <v>Checa dorsal</v>
-      </c>
-      <c r="D392">
-        <v>74</v>
+        <v>Thomas</v>
+      </c>
+      <c r="D392" t="str">
+        <v>EV</v>
       </c>
       <c r="E392">
         <v>2</v>
       </c>
       <c r="F392" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G392">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H392" t="str">
         <v/>
@@ -33342,19 +33342,19 @@
         <v>ARZON</v>
       </c>
       <c r="C393" t="str">
-        <v>1/4 Splindle</v>
+        <v>Checa dorsal</v>
       </c>
       <c r="D393">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="E393">
         <v>2</v>
       </c>
       <c r="F393" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G393">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H393" t="str">
         <v/>
@@ -33368,19 +33368,19 @@
         <v>ARZON</v>
       </c>
       <c r="C394" t="str">
-        <v>Molino Lateral</v>
+        <v xml:space="preserve">Stockli </v>
       </c>
       <c r="D394">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E394">
         <v>2</v>
       </c>
       <c r="F394" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G394">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H394" t="str">
         <v/>
@@ -34382,13 +34382,13 @@
         <v>ARZON</v>
       </c>
       <c r="C433" t="str">
-        <v>1/2 Magyar</v>
+        <v>Checa dorsal</v>
       </c>
       <c r="D433">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E433">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F433" t="str">
         <v>B</v>
@@ -34408,13 +34408,13 @@
         <v>ARZON</v>
       </c>
       <c r="C434" t="str">
-        <v>1/2 Sivado</v>
+        <v xml:space="preserve">Stockli </v>
       </c>
       <c r="D434">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E434">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F434" t="str">
         <v>B</v>
@@ -34434,13 +34434,13 @@
         <v>ARZON</v>
       </c>
       <c r="C435" t="str">
-        <v>Checa dorsal</v>
+        <v>1/2 Magyar</v>
       </c>
       <c r="D435">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E435">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F435" t="str">
         <v>B</v>
@@ -34460,13 +34460,13 @@
         <v>ARZON</v>
       </c>
       <c r="C436" t="str">
-        <v>1/2 Splindle</v>
+        <v>1/2 Sivado</v>
       </c>
       <c r="D436">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E436">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F436" t="str">
         <v>B</v>
@@ -34720,16 +34720,16 @@
         <v>SALTO</v>
       </c>
       <c r="C446" t="str">
-        <v>Tsukahara en C</v>
+        <v>Tsukahara en carpa</v>
       </c>
       <c r="D446">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E446">
         <v>3</v>
       </c>
       <c r="F446">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G446">
         <v>0</v>
@@ -38484,13 +38484,13 @@
         <v>AA NP</v>
       </c>
       <c r="F1" t="str">
-        <v>76.2</v>
+        <v>76.4</v>
       </c>
       <c r="G1" t="str">
         <v>AA</v>
       </c>
       <c r="H1" t="str">
-        <v>67.4</v>
+        <v>67.6</v>
       </c>
       <c r="I1" t="str">
         <v>77.07%</v>
@@ -39317,13 +39317,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>1/2 Magyar</v>
+        <v>Checa dorsal</v>
       </c>
       <c r="B17">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
         <v>B</v>
@@ -39332,7 +39332,7 @@
         <v>0.2</v>
       </c>
       <c r="F17" t="str">
-        <v>III</v>
+        <v>II</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -39370,13 +39370,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1/2 Sivado</v>
+        <v xml:space="preserve">Stockli </v>
       </c>
       <c r="B18">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="str">
         <v>B</v>
@@ -39385,7 +39385,7 @@
         <v>0.2</v>
       </c>
       <c r="F18" t="str">
-        <v>III</v>
+        <v>II</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -39423,13 +39423,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Checa dorsal</v>
+        <v>1/2 Magyar</v>
       </c>
       <c r="B19">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="str">
         <v>B</v>
@@ -39438,7 +39438,7 @@
         <v>0.2</v>
       </c>
       <c r="F19" t="str">
-        <v>II</v>
+        <v>III</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -39476,13 +39476,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1/2 Splindle</v>
+        <v>1/2 Sivado</v>
       </c>
       <c r="B20">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="str">
         <v>B</v>
@@ -39491,7 +39491,7 @@
         <v>0.2</v>
       </c>
       <c r="F20" t="str">
-        <v>II</v>
+        <v>III</v>
       </c>
       <c r="G20" t="str">
         <v>BPS</v>
@@ -40218,25 +40218,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Tsukahara en C</v>
+        <v>Tsukahara en carpa</v>
       </c>
       <c r="B34">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="G34">
-        <v>10.899999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -47100,13 +47100,13 @@
         <v>AA NP</v>
       </c>
       <c r="E1" t="str">
-        <v>73.7</v>
+        <v>73.5</v>
       </c>
       <c r="F1" t="str">
         <v>AA</v>
       </c>
       <c r="G1" t="str">
-        <v>67.7</v>
+        <v>64.7</v>
       </c>
       <c r="H1" t="str">
         <v>76.41%</v>
@@ -47161,10 +47161,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F3">
-        <v>1.2</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="G3">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -47222,7 +47222,7 @@
         <v>1.4</v>
       </c>
       <c r="G5">
-        <v>11.6</v>
+        <v>10.9</v>
       </c>
       <c r="H5">
         <v>0.5</v>
@@ -47291,10 +47291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Arabesca</v>
+        <v>Flic facial</v>
       </c>
       <c r="B8">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -47320,19 +47320,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Giro al frente extendido</v>
+        <v>Arabesca</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="E9">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -47541,7 +47541,7 @@
         <v>1.2</v>
       </c>
       <c r="G16">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="H16">
         <v>0.7</v>
@@ -47831,7 +47831,7 @@
         <v>1.3</v>
       </c>
       <c r="G26">
-        <v>11.600000000000001</v>
+        <v>11.100000000000001</v>
       </c>
       <c r="H26">
         <v>0.9</v>
@@ -48092,7 +48092,7 @@
         <v>12</v>
       </c>
       <c r="G35">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="H35">
         <v>0.6</v>
@@ -48208,7 +48208,7 @@
         <v>1.2</v>
       </c>
       <c r="G39">
-        <v>11.299999999999999</v>
+        <v>10.799999999999999</v>
       </c>
       <c r="H39">
         <v>0.7</v>
@@ -48498,7 +48498,7 @@
         <v>1</v>
       </c>
       <c r="G49">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H49">
         <v>0.8</v>
@@ -48694,25 +48694,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>65</v>
+      </c>
+      <c r="B1" t="str">
         <v>YERIK</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>__EMPTY</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>N 9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>AA NP</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>73.8</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>AA</v>
-      </c>
-      <c r="G1" t="str">
-        <v>67.8</v>
       </c>
       <c r="H1" t="str">
         <v>70.97%</v>
@@ -48723,25 +48723,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B2" t="str">
         <v>PISO</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
       <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
         <v>YERIK</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G2" t="str">
-        <v>NP</v>
       </c>
       <c r="H2" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -48751,26 +48751,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3">
+        <v>12.700000000000001</v>
+      </c>
+      <c r="B3" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1.3</v>
-      </c>
-      <c r="G3">
-        <v>12.700000000000001</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -48781,25 +48781,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B4" t="str">
         <v>Doble en c atrás</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
         <v>C</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.3</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>GRUPOS</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Probable NF</v>
       </c>
       <c r="H4">
         <v>0.95</v>
@@ -48809,26 +48809,26 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5">
+        <v>11.200000000000001</v>
+      </c>
+      <c r="B5" t="str">
         <v>Resorte</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="D5" t="str">
-        <v>A</v>
-      </c>
-      <c r="E5">
+      <c r="E5" t="str">
+        <v>A</v>
+      </c>
+      <c r="F5">
         <v>0.1</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>1.4</v>
-      </c>
-      <c r="G5">
-        <v>11.700000000000001</v>
       </c>
       <c r="H5">
         <v>0.6</v>
@@ -48839,22 +48839,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
         <v>Mortal Ext ade</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>B</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.2</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -48868,22 +48868,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
         <v>Giro atrás LC</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>4</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>B</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.2</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -48897,22 +48897,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
         <v>Arabesca</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>61</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="D8" t="str">
-        <v>A</v>
-      </c>
-      <c r="E8">
+      <c r="E8" t="str">
+        <v>A</v>
+      </c>
+      <c r="F8">
         <v>0.1</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -48926,22 +48926,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
         <v>Flic facial</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>67</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="D9" t="str">
-        <v>A</v>
-      </c>
-      <c r="E9">
+      <c r="E9" t="str">
+        <v>A</v>
+      </c>
+      <c r="F9">
         <v>0.1</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -48955,25 +48955,25 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
         <v>Flick Flack</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>13</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>3</v>
       </c>
-      <c r="D10" t="str">
-        <v>A</v>
-      </c>
-      <c r="E10">
+      <c r="E10" t="str">
+        <v>A</v>
+      </c>
+      <c r="F10">
         <v>0.1</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>BPP</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
       </c>
       <c r="H10">
         <v>0.95</v>
@@ -48984,22 +48984,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
         <v>Mortal Ext atrás</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>3</v>
       </c>
-      <c r="D11" t="str">
+      <c r="E11" t="str">
         <v>B</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.2</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -49013,25 +49013,25 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B12" t="str">
         <v>ARZONES</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
       <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
         <v>YERIK</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G12" t="str">
-        <v>NP</v>
       </c>
       <c r="H12" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -49041,26 +49041,26 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13">
+        <v>11.799999999999999</v>
+      </c>
+      <c r="B13" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B13" t="str">
+      <c r="C13" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C13" t="str">
+      <c r="D13" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D13" t="str">
+      <c r="E13" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.6</v>
-      </c>
-      <c r="G13">
-        <v>11.799999999999999</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -49071,25 +49071,25 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B14" t="str">
         <v xml:space="preserve">Corte tijera </v>
-      </c>
-      <c r="B14">
-        <v>1</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
-      <c r="D14" t="str">
-        <v>A</v>
-      </c>
-      <c r="E14">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>A</v>
+      </c>
+      <c r="F14">
         <v>0.1</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>GRUPOS</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Probable NF</v>
       </c>
       <c r="H14">
         <v>0.8</v>
@@ -49099,26 +49099,26 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="A15">
+        <v>10.299999999999999</v>
+      </c>
+      <c r="B15" t="str">
         <v>Molino en arzones</v>
       </c>
-      <c r="B15">
+      <c r="C15">
         <v>1</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>2</v>
       </c>
-      <c r="D15" t="str">
-        <v>A</v>
-      </c>
-      <c r="E15">
+      <c r="E15" t="str">
+        <v>A</v>
+      </c>
+      <c r="F15">
         <v>0.1</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>1.2</v>
-      </c>
-      <c r="G15">
-        <v>10.799999999999999</v>
       </c>
       <c r="H15">
         <v>0.65</v>
@@ -49129,19 +49129,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v/>
+      </c>
+      <c r="B16" t="str">
         <v>Molino en arzones</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>1</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>2</v>
       </c>
-      <c r="D16" t="str">
-        <v>A</v>
-      </c>
       <c r="E16" t="str">
-        <v/>
+        <v>A</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -49158,22 +49158,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v/>
+      </c>
+      <c r="B17" t="str">
         <v>Bajada lateral</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>1</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>3</v>
       </c>
-      <c r="D17" t="str">
-        <v>A</v>
-      </c>
-      <c r="E17">
+      <c r="E17" t="str">
+        <v>A</v>
+      </c>
+      <c r="F17">
         <v>0.1</v>
-      </c>
-      <c r="F17" t="str">
-        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -49187,22 +49187,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
         <v>Molino</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>7</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>2</v>
       </c>
-      <c r="D18" t="str">
-        <v>A</v>
-      </c>
-      <c r="E18">
+      <c r="E18" t="str">
+        <v>A</v>
+      </c>
+      <c r="F18">
         <v>0.1</v>
-      </c>
-      <c r="F18" t="str">
-        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -49216,19 +49216,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="B19" t="str">
         <v>1/4 de kher</v>
       </c>
-      <c r="B19" t="str">
+      <c r="C19" t="str">
         <v>EV</v>
       </c>
-      <c r="C19" t="str">
+      <c r="D19" t="str">
         <v>X</v>
       </c>
-      <c r="D19" t="str">
-        <v>A</v>
-      </c>
       <c r="E19" t="str">
-        <v/>
+        <v>A</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -49245,22 +49245,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
         <v>1/4 Splindle</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>25</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>2</v>
       </c>
-      <c r="D20" t="str">
-        <v>A</v>
-      </c>
-      <c r="E20">
+      <c r="E20" t="str">
+        <v>A</v>
+      </c>
+      <c r="F20">
         <v>0.1</v>
-      </c>
-      <c r="F20" t="str">
-        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -49274,22 +49274,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
         <v>Finlandesa</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>1</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>4</v>
       </c>
-      <c r="D21" t="str">
-        <v>A</v>
-      </c>
-      <c r="E21">
+      <c r="E21" t="str">
+        <v>A</v>
+      </c>
+      <c r="F21">
         <v>0.1</v>
-      </c>
-      <c r="F21" t="str">
-        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -49303,25 +49303,25 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B22" t="str">
         <v>ANILLOS</v>
       </c>
-      <c r="B22" t="str">
-        <v/>
-      </c>
       <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
         <v>YERIK</v>
       </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G22" t="str">
-        <v>NP</v>
       </c>
       <c r="H22" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -49331,26 +49331,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
+      <c r="A23">
+        <v>12.8</v>
+      </c>
+      <c r="B23" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B23" t="str">
+      <c r="C23" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C23" t="str">
+      <c r="D23" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D23" t="str">
+      <c r="E23" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E23" t="str">
+      <c r="F23" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>1.4000000000000001</v>
-      </c>
-      <c r="G23">
-        <v>12.8</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -49361,25 +49361,25 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B24" t="str">
         <v>Dislocada</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>25</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>1</v>
       </c>
-      <c r="D24" t="str">
-        <v>A</v>
-      </c>
-      <c r="E24">
+      <c r="E24" t="str">
+        <v>A</v>
+      </c>
+      <c r="F24">
         <v>0.1</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>GRUPOS</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Probable NF</v>
       </c>
       <c r="H24">
         <v>0.9</v>
@@ -49389,26 +49389,26 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
+      <c r="A25">
+        <v>11.3</v>
+      </c>
+      <c r="B25" t="str">
         <v>Dominada adelante a Lsit</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>2</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>3</v>
       </c>
-      <c r="D25" t="str">
+      <c r="E25" t="str">
         <v>B</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.2</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>1.4</v>
-      </c>
-      <c r="G25">
-        <v>11.8</v>
       </c>
       <c r="H25">
         <v>0.9</v>
@@ -49419,22 +49419,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="B26" t="str">
         <v>Rodada extendida adel</v>
       </c>
-      <c r="B26">
+      <c r="C26">
         <v>7</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>1</v>
       </c>
-      <c r="D26" t="str">
-        <v>A</v>
-      </c>
-      <c r="E26">
+      <c r="E26" t="str">
+        <v>A</v>
+      </c>
+      <c r="F26">
         <v>0.1</v>
-      </c>
-      <c r="F26" t="str">
-        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -49448,22 +49448,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
         <v>Inglesa</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>31</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>1</v>
       </c>
-      <c r="D27" t="str">
-        <v>A</v>
-      </c>
-      <c r="E27">
+      <c r="E27" t="str">
+        <v>A</v>
+      </c>
+      <c r="F27">
         <v>0.1</v>
-      </c>
-      <c r="F27" t="str">
-        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -49477,22 +49477,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
         <v>L sit</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>1</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>2</v>
       </c>
-      <c r="D28" t="str">
-        <v>A</v>
-      </c>
-      <c r="E28">
+      <c r="E28" t="str">
+        <v>A</v>
+      </c>
+      <c r="F28">
         <v>0.1</v>
-      </c>
-      <c r="F28" t="str">
-        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -49506,22 +49506,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="B29" t="str">
         <v>Kato</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>26</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>2</v>
       </c>
-      <c r="D29" t="str">
+      <c r="E29" t="str">
         <v>B</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.2</v>
-      </c>
-      <c r="F29" t="str">
-        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -49535,25 +49535,25 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" t="str">
         <v>Molino sost</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>62</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>1</v>
       </c>
-      <c r="D30" t="str">
+      <c r="E30" t="str">
         <v>C</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.3</v>
       </c>
-      <c r="F30" t="str">
+      <c r="G30" t="str">
         <v>BPP</v>
-      </c>
-      <c r="G30" t="str">
-        <v/>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -49564,22 +49564,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v/>
+      </c>
+      <c r="B31" t="str">
         <v>Multiple agrupado atras</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>52</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>4</v>
       </c>
-      <c r="D31" t="str">
+      <c r="E31" t="str">
         <v>C</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.3</v>
-      </c>
-      <c r="F31" t="str">
-        <v/>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -49593,16 +49593,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
+        <v/>
+      </c>
+      <c r="B32" t="str">
         <v>SALTO DE CABALLO</v>
       </c>
-      <c r="B32" t="str">
-        <v/>
-      </c>
       <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
         <v>YERIK</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -49622,26 +49622,26 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B33" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B33" t="str">
+      <c r="C33" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C33" t="str">
+      <c r="D33" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D33" t="str">
+      <c r="E33" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E33" t="str">
+      <c r="F33" t="str">
         <v>NOTA D</v>
       </c>
-      <c r="F33" t="str">
+      <c r="G33" t="str">
         <v>SALTOS</v>
       </c>
-      <c r="G33" t="str">
-        <v>Probable NF</v>
-      </c>
       <c r="H33" t="str">
         <v/>
       </c>
@@ -49650,26 +49650,26 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
+      <c r="A34">
+        <v>10.7</v>
+      </c>
+      <c r="B34" t="str">
         <v>Tsukahara en carpa</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>308</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>3</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>2</v>
       </c>
-      <c r="E34" t="str">
-        <v/>
-      </c>
-      <c r="F34">
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34">
         <v>12</v>
-      </c>
-      <c r="G34">
-        <v>11</v>
       </c>
       <c r="H34">
         <v>0.6</v>
@@ -49680,25 +49680,25 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B35" t="str">
         <v>PARALELAS</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
-      </c>
       <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
         <v>YERIK</v>
       </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G35" t="str">
-        <v>NP</v>
       </c>
       <c r="H35" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -49708,26 +49708,26 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
+      <c r="A36">
+        <v>12.1</v>
+      </c>
+      <c r="B36" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B36" t="str">
+      <c r="C36" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C36" t="str">
+      <c r="D36" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D36" t="str">
+      <c r="E36" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E36" t="str">
+      <c r="F36" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="G36">
-        <v>12.1</v>
       </c>
       <c r="H36" t="str">
         <v/>
@@ -49738,26 +49738,26 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B37" t="str">
         <v xml:space="preserve">Alemana </v>
       </c>
-      <c r="B37">
+      <c r="C37">
         <v>73</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>3</v>
       </c>
-      <c r="D37" t="str">
-        <v>A</v>
-      </c>
-      <c r="E37">
+      <c r="E37" t="str">
+        <v>A</v>
+      </c>
+      <c r="F37">
         <v>0.1</v>
       </c>
-      <c r="F37" t="str">
+      <c r="G37" t="str">
         <v>GRUPOS</v>
       </c>
-      <c r="G37" t="str">
-        <v>Probable NF</v>
-      </c>
       <c r="H37" t="str">
         <v/>
       </c>
@@ -49766,26 +49766,26 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
+      <c r="A38">
+        <v>10.6</v>
+      </c>
+      <c r="B38" t="str">
         <v>L-sit</v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>7</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>2</v>
       </c>
-      <c r="D38" t="str">
-        <v>A</v>
-      </c>
-      <c r="E38">
+      <c r="E38" t="str">
+        <v>A</v>
+      </c>
+      <c r="F38">
         <v>0.1</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>1.2</v>
-      </c>
-      <c r="G38">
-        <v>11.1</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -49796,22 +49796,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
+        <v/>
+      </c>
+      <c r="B39" t="str">
         <v>Kato</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>8</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>2</v>
       </c>
-      <c r="D39" t="str">
+      <c r="E39" t="str">
         <v>B</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>0.2</v>
-      </c>
-      <c r="F39" t="str">
-        <v/>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -49825,22 +49825,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v/>
+      </c>
+      <c r="B40" t="str">
         <v>Balleston aleman braq</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>97</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>3</v>
       </c>
-      <c r="D40" t="str">
-        <v>A</v>
-      </c>
-      <c r="E40">
+      <c r="E40" t="str">
+        <v>A</v>
+      </c>
+      <c r="F40">
         <v>0.1</v>
-      </c>
-      <c r="F40" t="str">
-        <v/>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -49854,22 +49854,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
+        <v/>
+      </c>
+      <c r="B41" t="str">
         <v>Vuelo</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>1</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>2</v>
       </c>
-      <c r="D41" t="str">
-        <v>A</v>
-      </c>
-      <c r="E41">
+      <c r="E41" t="str">
+        <v>A</v>
+      </c>
+      <c r="F41">
         <v>0.1</v>
-      </c>
-      <c r="F41" t="str">
-        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -49883,22 +49883,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
+        <v/>
+      </c>
+      <c r="B42" t="str">
         <v>Cambio</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>91</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>2</v>
       </c>
-      <c r="D42" t="str">
-        <v>A</v>
-      </c>
-      <c r="E42">
+      <c r="E42" t="str">
+        <v>A</v>
+      </c>
+      <c r="F42">
         <v>0.1</v>
-      </c>
-      <c r="F42" t="str">
-        <v/>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -49912,25 +49912,25 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
+        <v/>
+      </c>
+      <c r="B43" t="str">
         <v xml:space="preserve">Braq Subida de pecho </v>
-      </c>
-      <c r="B43">
-        <v>1</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
-      <c r="D43" t="str">
-        <v>A</v>
-      </c>
-      <c r="E43">
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="str">
+        <v>A</v>
+      </c>
+      <c r="F43">
         <v>0.1</v>
       </c>
-      <c r="F43" t="str">
+      <c r="G43" t="str">
         <v>BPP</v>
-      </c>
-      <c r="G43" t="str">
-        <v/>
       </c>
       <c r="H43">
         <v>0.9</v>
@@ -49941,22 +49941,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
         <v>Mortal adelante carp lat</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>1</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>4</v>
       </c>
-      <c r="D44" t="str">
-        <v>A</v>
-      </c>
-      <c r="E44">
+      <c r="E44" t="str">
+        <v>A</v>
+      </c>
+      <c r="F44">
         <v>0.1</v>
-      </c>
-      <c r="F44" t="str">
-        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -49970,25 +49970,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B45" t="str">
         <v>FIJA</v>
       </c>
-      <c r="B45" t="str">
-        <v/>
-      </c>
       <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
         <v>YERIK</v>
       </c>
-      <c r="D45" t="str">
-        <v/>
-      </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G45" t="str">
-        <v>NP</v>
       </c>
       <c r="H45" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -49998,26 +49998,26 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
+      <c r="A46">
+        <v>12.4</v>
+      </c>
+      <c r="B46" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B46" t="str">
+      <c r="C46" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C46" t="str">
+      <c r="D46" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D46" t="str">
+      <c r="E46" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E46" t="str">
+      <c r="F46" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>1.1</v>
-      </c>
-      <c r="G46">
-        <v>12.4</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -50028,25 +50028,25 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B47" t="str">
         <v>Voronin</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>26</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>2</v>
       </c>
-      <c r="D47" t="str">
+      <c r="E47" t="str">
         <v>B</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>0.2</v>
       </c>
-      <c r="F47" t="str">
+      <c r="G47" t="str">
         <v>GRUPOS</v>
-      </c>
-      <c r="G47" t="str">
-        <v>Probable NF</v>
       </c>
       <c r="H47">
         <v>0.85</v>
@@ -50056,26 +50056,26 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
+      <c r="A48">
+        <v>10.9</v>
+      </c>
+      <c r="B48" t="str">
         <v>Alemana a manos</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <v>1</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>3</v>
       </c>
-      <c r="D48" t="str">
-        <v>A</v>
-      </c>
-      <c r="E48">
+      <c r="E48" t="str">
+        <v>A</v>
+      </c>
+      <c r="F48">
         <v>0.1</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>1.3</v>
-      </c>
-      <c r="G48">
-        <v>11.4</v>
       </c>
       <c r="H48">
         <v>0.85</v>
@@ -50086,22 +50086,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
+        <v/>
+      </c>
+      <c r="B49" t="str">
         <v>Gigante</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <v>13</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>1</v>
       </c>
-      <c r="D49" t="str">
-        <v>A</v>
-      </c>
-      <c r="E49">
+      <c r="E49" t="str">
+        <v>A</v>
+      </c>
+      <c r="F49">
         <v>0.1</v>
-      </c>
-      <c r="F49" t="str">
-        <v/>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -50115,22 +50115,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
+        <v/>
+      </c>
+      <c r="B50" t="str">
         <v>Gigante Saltado</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <v>44</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>1</v>
       </c>
-      <c r="D50" t="str">
+      <c r="E50" t="str">
         <v>B</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0.2</v>
-      </c>
-      <c r="F50" t="str">
-        <v/>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -50144,22 +50144,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
+        <v/>
+      </c>
+      <c r="B51" t="str">
         <v>Cambio directo</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>37</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>1</v>
       </c>
-      <c r="D51" t="str">
-        <v>A</v>
-      </c>
-      <c r="E51">
+      <c r="E51" t="str">
+        <v>A</v>
+      </c>
+      <c r="F51">
         <v>0.1</v>
-      </c>
-      <c r="F51" t="str">
-        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -50173,22 +50173,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
+        <v/>
+      </c>
+      <c r="B52" t="str">
         <v>Molino</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>13</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>1</v>
       </c>
-      <c r="D52" t="str">
-        <v>A</v>
-      </c>
-      <c r="E52">
+      <c r="E52" t="str">
+        <v>A</v>
+      </c>
+      <c r="F52">
         <v>0.1</v>
-      </c>
-      <c r="F52" t="str">
-        <v/>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -50202,25 +50202,25 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
+        <v/>
+      </c>
+      <c r="B53" t="str">
         <v>Cambio sencillo</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>7</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>1</v>
       </c>
-      <c r="D53" t="str">
-        <v>A</v>
-      </c>
-      <c r="E53">
+      <c r="E53" t="str">
+        <v>A</v>
+      </c>
+      <c r="F53">
         <v>0.1</v>
       </c>
-      <c r="F53" t="str">
+      <c r="G53" t="str">
         <v>BPP</v>
-      </c>
-      <c r="G53" t="str">
-        <v/>
       </c>
       <c r="H53">
         <v>0.8</v>
@@ -50231,22 +50231,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
+        <v/>
+      </c>
+      <c r="B54" t="str">
         <v>Doble agrupado atras</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>32</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>4</v>
       </c>
-      <c r="D54" t="str">
+      <c r="E54" t="str">
         <v>B</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>0.2</v>
-      </c>
-      <c r="F54" t="str">
-        <v/>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -50283,13 +50283,13 @@
         <v>AA NP</v>
       </c>
       <c r="E1" t="str">
-        <v>77.6</v>
+        <v>77.2</v>
       </c>
       <c r="F1" t="str">
         <v>AA</v>
       </c>
       <c r="G1" t="str">
-        <v>68.8</v>
+        <v>68.4</v>
       </c>
       <c r="H1" t="str">
         <v>77.07%</v>
@@ -50889,7 +50889,7 @@
         <v>0.6</v>
       </c>
       <c r="G13">
-        <v>12.2</v>
+        <v>11.799999999999999</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -50986,10 +50986,10 @@
         <v>0.1</v>
       </c>
       <c r="F15">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G15">
-        <v>10.7</v>
+        <v>10.299999999999999</v>
       </c>
       <c r="H15">
         <v>0.85</v>
@@ -52994,13 +52994,13 @@
         <v>AA NP</v>
       </c>
       <c r="E1" t="str">
-        <v>76.1</v>
+        <v>77.3</v>
       </c>
       <c r="F1" t="str">
         <v>AA</v>
       </c>
       <c r="G1" t="str">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
       <c r="H1" t="str">
         <v>67.07%</v>
@@ -53091,10 +53091,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G3">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -53188,7 +53188,7 @@
         <v>1.4</v>
       </c>
       <c r="G5">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="H5">
         <v>0.5</v>
@@ -53264,10 +53264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Circulo en suelo</v>
+        <v>Arabesca</v>
       </c>
       <c r="B7">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -53311,19 +53311,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Arabesca</v>
+        <v>Giro al frente extendido</v>
       </c>
       <c r="B8">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="E8">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -53358,7 +53358,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Giro ext atrás</v>
+        <v>Giro ext atrás LC</v>
       </c>
       <c r="B9">
         <v>9</v>
@@ -54533,25 +54533,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Tsukahara en carpa</v>
+        <v>Tsukahara ext</v>
       </c>
       <c r="B34">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="G34">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
       <c r="H34">
         <v>0.5</v>
@@ -55112,10 +55112,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F46">
-        <v>1.3</v>
+        <v>1.5000000000000002</v>
       </c>
       <c r="G46">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -55209,7 +55209,7 @@
         <v>1.5</v>
       </c>
       <c r="G48">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H48">
         <v>0.85</v>
@@ -55332,19 +55332,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Cambio sencillo</v>
+        <v>Endo cerrado</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D51" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="E51">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F51" t="str">
         <v/>
